--- a/Planification_41_SAV_PROD.xlsx
+++ b/Planification_41_SAV_PROD.xlsx
@@ -9,11 +9,14 @@
   <sheets>
     <sheet name="Synthèse" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Grille hebdo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Contrôle secteurs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Demande 41" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Moteur dispo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Distances" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Planning SAV secteur" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Planning PROD secteur" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Contrôle secteur" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Contrôle secteurs" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Effectif" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Demande 41" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Moteur dispo" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Distances" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +102,42 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A5AA8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A04A18"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A7D0A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -157,8 +194,28 @@
         <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004D5D6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4EEFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEEE6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -180,11 +237,88 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -300,6 +434,46 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,7 +877,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -920,7 +1093,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -1054,8 +1226,9 @@
         <f>IF($C$24&gt;=$C$23,"TENABLE À "&amp;TEXT($B$13,"0")&amp;" TECHNICIENS — réserve de "&amp;TEXT($C$24-$C$23,"0")&amp;" créneaux, soit "&amp;TEXT(($C$24-$C$23)/$B$8,"0.0")&amp;" jours-technicien","INSUFFISANT — il manque "&amp;TEXT($C$23-$C$24,"0")&amp;" créneaux")</f>
         <v/>
       </c>
-    </row>
-    <row r="27"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="45" t="n"/>
+    </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1107,6 +1280,799 @@
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COHÉRENCE GÉOGRAPHIQUE — DISTANCES ROUTIÈRES ESTIMÉES (km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Estimation : vol d'oiseau × 1,25, majorée de 8 km entre les deux rives de la Loire (ponts de Blois, Chaumont, Muides, Beaugency). À recaler avec votre outil de tournées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="G4" s="39" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="I4" s="39" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="J4" s="39" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="K4" s="39" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="L4" s="39" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="M4" s="39" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="J5" s="42" t="n">
+        <v>65</v>
+      </c>
+      <c r="K5" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="L5" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="M5" s="42" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" s="41" t="n">
+        <v>47</v>
+      </c>
+      <c r="J6" s="42" t="n">
+        <v>84</v>
+      </c>
+      <c r="K6" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" s="42" t="n">
+        <v>67</v>
+      </c>
+      <c r="M6" s="42" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="n">
+        <v>66</v>
+      </c>
+      <c r="F7" s="42" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="42" t="n">
+        <v>70</v>
+      </c>
+      <c r="H7" s="42" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" s="42" t="n">
+        <v>52</v>
+      </c>
+      <c r="J7" s="42" t="n">
+        <v>81</v>
+      </c>
+      <c r="K7" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="L7" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="M7" s="42" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C8" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>66</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>99</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>96</v>
+      </c>
+      <c r="M8" s="42" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="I9" s="41" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>70</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>65</v>
+      </c>
+      <c r="L9" s="42" t="n">
+        <v>74</v>
+      </c>
+      <c r="M9" s="42" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>70</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>48</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>78</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>117</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>95</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="M10" s="42" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="C11" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>90</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>78</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>113</v>
+      </c>
+      <c r="K11" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>118</v>
+      </c>
+      <c r="M11" s="42" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="C12" s="41" t="n">
+        <v>47</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>52</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" s="41" t="n">
+        <v>33</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>78</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>78</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="K12" s="41" t="n">
+        <v>41</v>
+      </c>
+      <c r="L12" s="41" t="n">
+        <v>47</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="n">
+        <v>65</v>
+      </c>
+      <c r="C13" s="42" t="n">
+        <v>84</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>81</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>99</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>117</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>113</v>
+      </c>
+      <c r="I13" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="L13" s="41" t="n">
+        <v>49</v>
+      </c>
+      <c r="M13" s="41" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C14" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>65</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>95</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="I14" s="41" t="n">
+        <v>41</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="41" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="C15" s="42" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>96</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>74</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>118</v>
+      </c>
+      <c r="I15" s="41" t="n">
+        <v>47</v>
+      </c>
+      <c r="J15" s="41" t="n">
+        <v>49</v>
+      </c>
+      <c r="K15" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="34" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="n">
+        <v>66</v>
+      </c>
+      <c r="C16" s="42" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>68</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>110</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>84</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>123</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>129</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>52</v>
+      </c>
+      <c r="J16" s="41" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="L16" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Vert ≤ 30 km : enchaînement de deux demi-journées acceptable   ·   Orange 31-50 km : à éviter dans la même journée   ·   Rouge &gt; 50 km : incohérent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ENCHAÎNEMENTS RETENUS DANS LA GRILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Matin</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Après-midi</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Techniciens concernés</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>30 km</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>T2 mardi, jeudi, samedi · T9 mardi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>29 km</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>T2 lundi, mercredi, vendredi · T9 lundi, mercredi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>29 km</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>T11 mardi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>22 km</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>T3 mardi, jeudi, samedi · T10 vendredi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>13 km</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>T10 lundi, mercredi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -1162,7 +2128,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -2320,7 +3285,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
+      <c r="B17" s="45" t="n"/>
       <c r="C17" s="4">
         <f>SUM(C6:C16)</f>
         <v/>
@@ -2350,7 +3315,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -2382,6 +3346,3061 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PLANNING SAV SECTEUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Créneaux réservés au SAV, ouverts à la prise de rendez-vous J+1/J+2. Format « T2·4 » = technicien T2, 4 créneaux. Chaque secteur doit apparaître 3 fois par semaine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="n"/>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="I4" s="47" t="n"/>
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="K4" s="47" t="n"/>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="M4" s="47" t="n"/>
+      <c r="N4" s="46" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="O4" s="46" t="inlineStr">
+        <is>
+          <t>Demandé</t>
+        </is>
+      </c>
+      <c r="P4" s="46" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="n"/>
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="H5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="K5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="L5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="M5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="47" t="n"/>
+      <c r="P5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4 T6·4</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>T6·4</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4 T6·4</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>T6·4</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4 T6·4</t>
+        </is>
+      </c>
+      <c r="K6" s="51" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="L6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="O6" s="52" t="n">
+        <v>42</v>
+      </c>
+      <c r="P6" s="31">
+        <f>IF($N6&gt;=$O6,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="H7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="K7" s="51" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="L7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="O7" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="P7" s="31">
+        <f>IF($N7&gt;=$O7,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="51" t="inlineStr">
+        <is>
+          <t>T4·3</t>
+        </is>
+      </c>
+      <c r="K8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" s="31">
+        <f>IF($N8&gt;=$O8,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="H9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="51" t="inlineStr">
+        <is>
+          <t>T2·3</t>
+        </is>
+      </c>
+      <c r="L9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="P9" s="31">
+        <f>IF($N9&gt;=$O9,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>T3·4</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>T3·4</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="H10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="51" t="inlineStr">
+        <is>
+          <t>T3·4</t>
+        </is>
+      </c>
+      <c r="K10" s="51" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="L10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" s="31">
+        <f>IF($N10&gt;=$O10,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="51" t="inlineStr">
+        <is>
+          <t>T2·3</t>
+        </is>
+      </c>
+      <c r="M11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" s="31">
+        <f>IF($N11&gt;=$O11,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>T3·3</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>T3·3</t>
+        </is>
+      </c>
+      <c r="I12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="51" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="M12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" s="31">
+        <f>IF($N12&gt;=$O12,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>T1·3</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>T1·3</t>
+        </is>
+      </c>
+      <c r="I13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>T1·3</t>
+        </is>
+      </c>
+      <c r="M13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" s="31">
+        <f>IF($N13&gt;=$O13,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>T2·4</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" s="31">
+        <f>IF($N14&gt;=$O14,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>T4·3</t>
+        </is>
+      </c>
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>T4·3</t>
+        </is>
+      </c>
+      <c r="I15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>T4·3</t>
+        </is>
+      </c>
+      <c r="M15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" s="31">
+        <f>IF($N15&gt;=$O15,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>T2·3</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="51" t="inlineStr">
+        <is>
+          <t>T2·3</t>
+        </is>
+      </c>
+      <c r="J16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>T2·3</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="31">
+        <f>IF($N16&gt;=$O16,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="51" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="J17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" s="31">
+        <f>IF($N17&gt;=$O17,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>12 secteurs · les totaux se recoupent avec l'onglet « Grille hebdo »</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4">
+        <f>SUM(N6:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>SUM(O6:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>COUNTIF(P6:P17,"OK")&amp;" / 12"</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PLANNING PROD SECTEUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Créneaux ouverts à la production, posés depuis le carnet J+5/J+7. Ils occupent tout ce que le SAV ne réserve pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="n"/>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="I4" s="47" t="n"/>
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="K4" s="47" t="n"/>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="M4" s="47" t="n"/>
+      <c r="N4" s="46" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="O4" s="46" t="inlineStr">
+        <is>
+          <t>Demandé</t>
+        </is>
+      </c>
+      <c r="P4" s="46" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="n"/>
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="H5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="K5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="L5" s="49" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
+      <c r="M5" s="49" t="inlineStr">
+        <is>
+          <t>après-midi</t>
+        </is>
+      </c>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="47" t="n"/>
+      <c r="P5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>T7·4 T8·4 T11·4</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>T6·4 T7·4 T8·4 T11·4</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>T6·4 T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>T7·4 T8·4 T11·4</t>
+        </is>
+      </c>
+      <c r="G6" s="54" t="inlineStr">
+        <is>
+          <t>T6·4 T7·4 T8·4 T11·4</t>
+        </is>
+      </c>
+      <c r="H6" s="54" t="inlineStr">
+        <is>
+          <t>T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="I6" s="54" t="inlineStr">
+        <is>
+          <t>T6·4 T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="J6" s="54" t="inlineStr">
+        <is>
+          <t>T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="K6" s="54" t="inlineStr">
+        <is>
+          <t>T6·4 T7·4 T8·4</t>
+        </is>
+      </c>
+      <c r="L6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="O6" s="52" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P6" s="31">
+        <f>IF($N6&gt;=$O6,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4 T10·4</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4 T10·4</t>
+        </is>
+      </c>
+      <c r="F7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4 T10·4</t>
+        </is>
+      </c>
+      <c r="I7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4 T10·4</t>
+        </is>
+      </c>
+      <c r="J7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="M7" s="54" t="inlineStr">
+        <is>
+          <t>T5·4</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="O7" s="52" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P7" s="31">
+        <f>IF($N7&gt;=$O7,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="54" t="inlineStr">
+        <is>
+          <t>T4·1 T11·4</t>
+        </is>
+      </c>
+      <c r="K8" s="54" t="inlineStr">
+        <is>
+          <t>T4·4 T11·4</t>
+        </is>
+      </c>
+      <c r="L8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="O8" s="52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="P8" s="31">
+        <f>IF($N8&gt;=$O8,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>T11·4</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="H9" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="J9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="54" t="inlineStr">
+        <is>
+          <t>T2·1</t>
+        </is>
+      </c>
+      <c r="L9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="O9" s="52" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P9" s="31">
+        <f>IF($N9&gt;=$O9,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>T3·3 T10·4</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="54" t="inlineStr">
+        <is>
+          <t>T3·3 T10·4</t>
+        </is>
+      </c>
+      <c r="H10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="54" t="inlineStr">
+        <is>
+          <t>T3·3</t>
+        </is>
+      </c>
+      <c r="L10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="O10" s="52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P10" s="31">
+        <f>IF($N10&gt;=$O10,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="54" t="inlineStr">
+        <is>
+          <t>T11·4</t>
+        </is>
+      </c>
+      <c r="I11" s="54" t="inlineStr">
+        <is>
+          <t>T11·4</t>
+        </is>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="K11" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="L11" s="54" t="inlineStr">
+        <is>
+          <t>T2·1</t>
+        </is>
+      </c>
+      <c r="M11" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" s="52" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P11" s="31">
+        <f>IF($N11&gt;=$O11,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>T10·4</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="54" t="inlineStr">
+        <is>
+          <t>T10·4</t>
+        </is>
+      </c>
+      <c r="G12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>T3·1</t>
+        </is>
+      </c>
+      <c r="I12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>T10·4</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="54" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="M12" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="O12" s="52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="P12" s="31">
+        <f>IF($N12&gt;=$O12,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>T1·1</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="54" t="inlineStr">
+        <is>
+          <t>T1·1</t>
+        </is>
+      </c>
+      <c r="I13" s="54" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="J13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="54" t="inlineStr">
+        <is>
+          <t>T1·1</t>
+        </is>
+      </c>
+      <c r="M13" s="54" t="inlineStr">
+        <is>
+          <t>T1·4</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" s="52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P13" s="31">
+        <f>IF($N13&gt;=$O13,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>T11·4</t>
+        </is>
+      </c>
+      <c r="F14" s="54" t="inlineStr">
+        <is>
+          <t>T9·4</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P14" s="31">
+        <f>IF($N14&gt;=$O14,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>T4·1</t>
+        </is>
+      </c>
+      <c r="E15" s="54" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="54" t="inlineStr">
+        <is>
+          <t>T4·1</t>
+        </is>
+      </c>
+      <c r="I15" s="54" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="J15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="54" t="inlineStr">
+        <is>
+          <t>T4·1</t>
+        </is>
+      </c>
+      <c r="M15" s="54" t="inlineStr">
+        <is>
+          <t>T4·4</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" s="52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P15" s="31">
+        <f>IF($N15&gt;=$O15,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="54" t="inlineStr">
+        <is>
+          <t>T2·1 T9·4</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="54" t="inlineStr">
+        <is>
+          <t>T2·1</t>
+        </is>
+      </c>
+      <c r="J16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="54" t="inlineStr">
+        <is>
+          <t>T2·1</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P16" s="31">
+        <f>IF($N16&gt;=$O16,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="54" t="inlineStr">
+        <is>
+          <t>T3·2</t>
+        </is>
+      </c>
+      <c r="J17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="54" t="inlineStr">
+        <is>
+          <t>T10·4</t>
+        </is>
+      </c>
+      <c r="L17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="54" t="inlineStr">
+        <is>
+          <t>T3·3</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" s="52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P17" s="31">
+        <f>IF($N17&gt;=$O17,"OK","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>12 secteurs · les totaux se recoupent avec l'onglet « Grille hebdo »</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4">
+        <f>SUM(N6:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>SUM(O6:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>COUNTIF(P6:P17,"OK")&amp;" / 12"</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRÔLE PAR SECTEUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Trois conditions : au moins 3 passages SAV sur un rythme valide, réservation SAV ≥ demande, capacité PROD ≥ demande.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Jours de passage SAV</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Passages</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Rythme</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>SAV ouvert</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>SAV demandé</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>Marge SAV</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>PROD ouverte</t>
+        </is>
+      </c>
+      <c r="I4" s="46" t="inlineStr">
+        <is>
+          <t>PROD demandée</t>
+        </is>
+      </c>
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>Marge PROD</t>
+        </is>
+      </c>
+      <c r="K4" s="46" t="inlineStr">
+        <is>
+          <t>Total créneaux</t>
+        </is>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>Cible</t>
+        </is>
+      </c>
+      <c r="M4" s="46" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mar · Mer · Jeu · Ven</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>quotidien</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="52" t="n">
+        <v>42</v>
+      </c>
+      <c r="G5" s="57">
+        <f>$E5-$F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J5" s="59">
+        <f>$H5-$I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>$E5+$H5</f>
+        <v/>
+      </c>
+      <c r="L5" s="52" t="n">
+        <v>138</v>
+      </c>
+      <c r="M5" s="31">
+        <f>IF(AND($C5&gt;=3,$E5&gt;=$F5,$H5&gt;=$I5),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mer · Ven</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>L-Me-V</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="57">
+        <f>$E6-$F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="58" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J6" s="59">
+        <f>$H6-$I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>$E6+$H6</f>
+        <v/>
+      </c>
+      <c r="L6" s="52" t="n">
+        <v>62</v>
+      </c>
+      <c r="M6" s="31">
+        <f>IF(AND($C6&gt;=3,$E6&gt;=$F6,$H6&gt;=$I6),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mer · Ven</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>L-Me-V</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="57">
+        <f>$E7-$F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" s="58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J7" s="59">
+        <f>$H7-$I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>$E7+$H7</f>
+        <v/>
+      </c>
+      <c r="L7" s="52" t="n">
+        <v>28</v>
+      </c>
+      <c r="M7" s="31">
+        <f>IF(AND($C7&gt;=3,$E7&gt;=$F7,$H7&gt;=$I7),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mer · Ven</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>L-Me-V</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="57">
+        <f>$E8-$F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" s="58" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J8" s="59">
+        <f>$H8-$I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>$E8+$H8</f>
+        <v/>
+      </c>
+      <c r="L8" s="52" t="n">
+        <v>32</v>
+      </c>
+      <c r="M8" s="31">
+        <f>IF(AND($C8&gt;=3,$E8&gt;=$F8,$H8&gt;=$I8),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mer · Ven</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>L-Me-V</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="57">
+        <f>$E9-$F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" s="58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J9" s="59">
+        <f>$H9-$I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>$E9+$H9</f>
+        <v/>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="M9" s="31">
+        <f>IF(AND($C9&gt;=3,$E9&gt;=$F9,$H9&gt;=$I9),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="57">
+        <f>$E10-$F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I10" s="58" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J10" s="59">
+        <f>$H10-$I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>$E10+$H10</f>
+        <v/>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" s="31">
+        <f>IF(AND($C10&gt;=3,$E10&gt;=$F10,$H10&gt;=$I10),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="57">
+        <f>$E11-$F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" s="58" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J11" s="59">
+        <f>$H11-$I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>$E11+$H11</f>
+        <v/>
+      </c>
+      <c r="L11" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="M11" s="31">
+        <f>IF(AND($C11&gt;=3,$E11&gt;=$F11,$H11&gt;=$I11),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="57">
+        <f>$E12-$F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J12" s="59">
+        <f>$H12-$I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>$E12+$H12</f>
+        <v/>
+      </c>
+      <c r="L12" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="M12" s="31">
+        <f>IF(AND($C12&gt;=3,$E12&gt;=$F12,$H12&gt;=$I12),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>Lun · Mer · Ven</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>L-Me-V</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="57">
+        <f>$E13-$F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="58" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J13" s="59">
+        <f>$H13-$I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="21">
+        <f>$E13+$H13</f>
+        <v/>
+      </c>
+      <c r="L13" s="52" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="31">
+        <f>IF(AND($C13&gt;=3,$E13&gt;=$F13,$H13&gt;=$I13),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="57">
+        <f>$E14-$F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" s="58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J14" s="59">
+        <f>$H14-$I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>$E14+$H14</f>
+        <v/>
+      </c>
+      <c r="L14" s="52" t="n">
+        <v>21</v>
+      </c>
+      <c r="M14" s="31">
+        <f>IF(AND($C14&gt;=3,$E14&gt;=$F14,$H14&gt;=$I14),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="57">
+        <f>$E15-$F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="58" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" s="59">
+        <f>$H15-$I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>$E15+$H15</f>
+        <v/>
+      </c>
+      <c r="L15" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="M15" s="31">
+        <f>IF(AND($C15&gt;=3,$E15&gt;=$F15,$H15&gt;=$I15),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>Mar · Jeu · Sam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Ma-J-S</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="57">
+        <f>$E16-$F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="59">
+        <f>$H16-$I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>$E16+$H16</f>
+        <v/>
+      </c>
+      <c r="L16" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" s="31">
+        <f>IF(AND($C16&gt;=3,$E16&gt;=$F16,$H16&gt;=$I16),"conforme","À CORRIGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4">
+        <f>SUM(E5:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="32">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="32">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="4">
+        <f>COUNTIF(M5:M16,"conforme")&amp;" / 12"</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2419,7 +6438,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3128,7 +7146,6 @@
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -3140,2245 +7157,6 @@
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Un secteur peut dépasser sa cible : l'excédent constitue sa réserve locale. Il ne doit jamais passer sous la demande SAV ni sous la demande PROD.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMANDE PAR SECTEUR — DÉPARTEMENT 41</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Colonnes B à D : volumes bruts du fichier source. Colonne I (bleue) : volume SAV relevé sur votre planning hebdomadaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Secteur</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>PROD octobre
-(inter./mois)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>PROD mars
-(inter./mois)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>B2B
-(inter./mois)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mois retenu
-(max par secteur)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>PROD retenue
-+10 % (/mois)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>PROD
-+10 % (/sem.)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PROD
-(/sem.)</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>SAV
-(/sem.)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Demande totale
-(/sem.)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Créneaux cible
-(occupation 75 %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>240</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>218</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="10">
-        <f>MAX($B5,$C5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="30">
-        <f>($E5+$D5)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G5" s="30">
-        <f>$F5/4.3333</f>
-        <v/>
-      </c>
-      <c r="H5" s="30">
-        <f>$G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="J5" s="30">
-        <f>$H5+$I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="30">
-        <f>$J5/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E6" s="10">
-        <f>MAX($B6,$C6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="30">
-        <f>($E6+$D6)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G6" s="30">
-        <f>$F6/4.3333</f>
-        <v/>
-      </c>
-      <c r="H6" s="30">
-        <f>$G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J6" s="30">
-        <f>$H6+$I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="30">
-        <f>$J6/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E7" s="10">
-        <f>MAX($B7,$C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="30">
-        <f>($E7+$D7)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G7" s="30">
-        <f>$F7/4.3333</f>
-        <v/>
-      </c>
-      <c r="H7" s="30">
-        <f>$G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J7" s="30">
-        <f>$H7+$I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="30">
-        <f>$J7/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E8" s="10">
-        <f>MAX($B8,$C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="30">
-        <f>($E8+$D8)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G8" s="30">
-        <f>$F8/4.3333</f>
-        <v/>
-      </c>
-      <c r="H8" s="30">
-        <f>$G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="30">
-        <f>$H8+$I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="30">
-        <f>$J8/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E9" s="10">
-        <f>MAX($B9,$C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="30">
-        <f>($E9+$D9)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G9" s="30">
-        <f>$F9/4.3333</f>
-        <v/>
-      </c>
-      <c r="H9" s="30">
-        <f>$G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="30">
-        <f>$H9+$I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="30">
-        <f>$J9/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>Montoire-sur-le-Loir</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E10" s="10">
-        <f>MAX($B10,$C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="30">
-        <f>($E10+$D10)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G10" s="30">
-        <f>$F10/4.3333</f>
-        <v/>
-      </c>
-      <c r="H10" s="30">
-        <f>$G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="30">
-        <f>$H10+$I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="30">
-        <f>$J10/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="D11" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E11" s="10">
-        <f>MAX($B11,$C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="30">
-        <f>($E11+$D11)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G11" s="30">
-        <f>$F11/4.3333</f>
-        <v/>
-      </c>
-      <c r="H11" s="30">
-        <f>$G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" s="30">
-        <f>$H11+$I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="30">
-        <f>$J11/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E12" s="10">
-        <f>MAX($B12,$C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="30">
-        <f>($E12+$D12)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="30">
-        <f>$F12/4.3333</f>
-        <v/>
-      </c>
-      <c r="H12" s="30">
-        <f>$G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="30">
-        <f>$H12+$I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="30">
-        <f>$J12/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Valencisse</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E13" s="10">
-        <f>MAX($B13,$C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="30">
-        <f>($E13+$D13)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="30">
-        <f>$F13/4.3333</f>
-        <v/>
-      </c>
-      <c r="H13" s="30">
-        <f>$G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="30">
-        <f>$H13+$I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="30">
-        <f>$J13/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Vouzon</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E14" s="10">
-        <f>MAX($B14,$C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="30">
-        <f>($E14+$D14)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G14" s="30">
-        <f>$F14/4.3333</f>
-        <v/>
-      </c>
-      <c r="H14" s="30">
-        <f>$G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="30">
-        <f>$H14+$I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="30">
-        <f>$J14/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Cormenon</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="D15" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E15" s="10">
-        <f>MAX($B15,$C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="30">
-        <f>($E15+$D15)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G15" s="30">
-        <f>$F15/4.3333</f>
-        <v/>
-      </c>
-      <c r="H15" s="30">
-        <f>$G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="30">
-        <f>$H15+$I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="30">
-        <f>$J15/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>La Ferté-Imbault</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E16" s="10">
-        <f>MAX($B16,$C16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>($E16+$D16)*(1+Synthèse!$B$12)</f>
-        <v/>
-      </c>
-      <c r="G16" s="30">
-        <f>$F16/4.3333</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>$G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="30">
-        <f>$H16+$I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="30">
-        <f>$J16/Synthèse!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL DÉPARTEMENT 41</t>
-        </is>
-      </c>
-      <c r="B17" s="33">
-        <f>SUM(B5:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="33">
-        <f>SUM(C5:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>SUM(E5:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>SUM(F5:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>SUM(G5:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="32">
-        <f>SUM(H5:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="33">
-        <f>SUM(I5:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="32">
-        <f>SUM(J5:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="32">
-        <f>SUM(K5:K16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Le fichier source ne dimensionne que sur mars. Or sur le 41, octobre est le mois haut (705 interventions contre 656) : retenir le mois le plus chargé secteur par secteur ajoute environ 7 % au besoin.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MOTEUR DE DISPONIBILITÉ — RÉSERVATION SAV ET BASCULE PROD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Le mécanisme qui libère de la disponibilité sans embaucher : on réserve large pour le SAV, et tout créneau non vendu redevient de la PROD la veille au soir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>RÈGLES D'EXPLOITATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>N°</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Moment</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Règle</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Effet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>La tournée est figée : technicien × jour × secteur ne change jamais.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Distances maîtrisées, techniciens sur des secteurs qu'ils connaissent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>Chaque secteur est visité 3 fois par semaine, rythme Lundi-Mercredi-Vendredi ou Mardi-Jeudi-Samedi.</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Quel que soit le jour d'appel, il existe un passage à J+1 ou J+2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Sur chaque demi-journée, un nombre fixe de créneaux est réservé au SAV. Le reste est ouvert à la PROD.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>L'occupation ne dépasse jamais 75 % : le quart restant est la disponibilité.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>J-7 à J-5</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>La PROD se pose uniquement sur les créneaux non réservés au SAV, dans le carnet J+5 à J+7.</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Le client PROD obtient bien un RDV à J+5/J+6/J+7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>J-2, 18 h</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>Ouverture à la prise de RDV SAV des créneaux réservés du jour J.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Le client SAV qui appelle voit de la dispo à J+1 et J+2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>J-1, 18 h</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="inlineStr">
-        <is>
-          <t>BASCULE : tout créneau SAV encore libre pour le lendemain est réaffecté à une intervention PROD du même secteur.</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Aucun créneau perdu. C'est ce qui rend la réservation SAV quasi gratuite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>J-1, 18 h</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>La bascule suppose au moins 2 interventions PROD en attente dans le secteur.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Sur Cormenon et La Ferté-Imbault, maintenir un stock PROD tampon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Jour J</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>Un SAV urgent arrivé après la bascule prend la place d'une PROD du jour, qui repart en J+5.</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>La PROD absorbe l'aléa, jamais le SAV — c'est elle qui a le délai le plus long.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Hebdo</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>Si l'occupation SAV d'un secteur dépasse 75 % quatre semaines de suite, augmenter sa réservation.</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Le curseur de réservation suit la demande réelle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Hebdo</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>Le renfort flottant (T11) est affecté le vendredi pour la semaine suivante, au secteur au carnet le plus tendu.</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>La réserve va là où elle sert, pas là où elle dort.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>TABLEAU DE BORD QUOTIDIEN — À REMPLIR CHAQUE SOIR AVANT LA BASCULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Colonne D (jaune) : nombre de RDV SAV réellement pris pour le lendemain. Le reste se calcule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Secteur visité demain</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Créneaux du jour</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>dont réservés SAV</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>RDV SAV pris (à saisir)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Créneaux SAV libres</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>PROD à injecter</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Occupation SAV</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Alerte</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7">
-        <f>MAX(0,$C20-$D20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="7">
-        <f>$E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="37">
-        <f>IFERROR($D20/$C20,0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>IF($D20&gt;$C20,"Débordement SAV : basculer une PROD du jour",IF($D20/$C20&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F20,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7">
-        <f>MAX(0,$C21-$D21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="7">
-        <f>$E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="37">
-        <f>IFERROR($D21/$C21,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="8">
-        <f>IF($D21&gt;$C21,"Débordement SAV : basculer une PROD du jour",IF($D21/$C21&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F21,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7">
-        <f>MAX(0,$C22-$D22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="7">
-        <f>$E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="37">
-        <f>IFERROR($D22/$C22,0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="8">
-        <f>IF($D22&gt;$C22,"Débordement SAV : basculer une PROD du jour",IF($D22/$C22&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F22,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="7">
-        <f>MAX(0,$C23-$D23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="7">
-        <f>$E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="37">
-        <f>IFERROR($D23/$C23,0)</f>
-        <v/>
-      </c>
-      <c r="H23" s="8">
-        <f>IF($D23&gt;$C23,"Débordement SAV : basculer une PROD du jour",IF($D23/$C23&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F23,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7">
-        <f>MAX(0,$C24-$D24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="7">
-        <f>$E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="37">
-        <f>IFERROR($D24/$C24,0)</f>
-        <v/>
-      </c>
-      <c r="H24" s="8">
-        <f>IF($D24&gt;$C24,"Débordement SAV : basculer une PROD du jour",IF($D24/$C24&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F24,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7">
-        <f>MAX(0,$C25-$D25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="7">
-        <f>$E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="37">
-        <f>IFERROR($D25/$C25,0)</f>
-        <v/>
-      </c>
-      <c r="H25" s="8">
-        <f>IF($D25&gt;$C25,"Débordement SAV : basculer une PROD du jour",IF($D25/$C25&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F25,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Valencisse</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7">
-        <f>MAX(0,$C26-$D26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="7">
-        <f>$E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="37">
-        <f>IFERROR($D26/$C26,0)</f>
-        <v/>
-      </c>
-      <c r="H26" s="8">
-        <f>IF($D26&gt;$C26,"Débordement SAV : basculer une PROD du jour",IF($D26/$C26&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F26,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Montoire-sur-le-Loir</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7">
-        <f>MAX(0,$C27-$D27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="7">
-        <f>$E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="37">
-        <f>IFERROR($D27/$C27,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="8">
-        <f>IF($D27&gt;$C27,"Débordement SAV : basculer une PROD du jour",IF($D27/$C27&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F27,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>Cormenon</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7">
-        <f>MAX(0,$C28-$D28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="7">
-        <f>$E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="37">
-        <f>IFERROR($D28/$C28,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="8">
-        <f>IF($D28&gt;$C28,"Débordement SAV : basculer une PROD du jour",IF($D28/$C28&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F28,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7">
-        <f>MAX(0,$C29-$D29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="7">
-        <f>$E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="37">
-        <f>IFERROR($D29/$C29,0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="8">
-        <f>IF($D29&gt;$C29,"Débordement SAV : basculer une PROD du jour",IF($D29/$C29&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F29,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>La Ferté-Imbault</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7">
-        <f>MAX(0,$C30-$D30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="7">
-        <f>$E30</f>
-        <v/>
-      </c>
-      <c r="G30" s="37">
-        <f>IFERROR($D30/$C30,0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="8">
-        <f>IF($D30&gt;$C30,"Débordement SAV : basculer une PROD du jour",IF($D30/$C30&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F30,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Vouzon</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7">
-        <f>MAX(0,$C31-$D31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="7">
-        <f>$E31</f>
-        <v/>
-      </c>
-      <c r="G31" s="37">
-        <f>IFERROR($D31/$C31,0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="8">
-        <f>IF($D31&gt;$C31,"Débordement SAV : basculer une PROD du jour",IF($D31/$C31&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F31,"0")&amp;" PROD du carnet J+5/J+7"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL JOUR</t>
-        </is>
-      </c>
-      <c r="B32" s="4">
-        <f>SUM(B20:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="4">
-        <f>SUM(C20:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="4">
-        <f>SUM(D20:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="4">
-        <f>SUM(E20:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="4">
-        <f>SUM(F20:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="38">
-        <f>IFERROR($D32/$C32,0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>COHÉRENCE GÉOGRAPHIQUE — DISTANCES ROUTIÈRES ESTIMÉES (km)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Estimation : vol d'oiseau × 1,25, majorée de 8 km entre les deux rives de la Loire (ponts de Blois, Chaumont, Muides, Beaugency). À recaler avec votre outil de tournées.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="C4" s="39" t="inlineStr">
-        <is>
-          <t>Valencisse</t>
-        </is>
-      </c>
-      <c r="D4" s="39" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="F4" s="39" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="G4" s="39" t="inlineStr">
-        <is>
-          <t>Montoire-sur-le-Loir</t>
-        </is>
-      </c>
-      <c r="H4" s="39" t="inlineStr">
-        <is>
-          <t>Cormenon</t>
-        </is>
-      </c>
-      <c r="I4" s="39" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson</t>
-        </is>
-      </c>
-      <c r="J4" s="39" t="inlineStr">
-        <is>
-          <t>Vouzon</t>
-        </is>
-      </c>
-      <c r="K4" s="39" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne</t>
-        </is>
-      </c>
-      <c r="L4" s="39" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="M4" s="39" t="inlineStr">
-        <is>
-          <t>La Ferté-Imbault</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>Blois</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="G5" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" s="42" t="n">
-        <v>61</v>
-      </c>
-      <c r="I5" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="J5" s="42" t="n">
-        <v>65</v>
-      </c>
-      <c r="K5" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="L5" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="M5" s="42" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>Valencisse</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="41" t="n">
-        <v>35</v>
-      </c>
-      <c r="E6" s="41" t="n">
-        <v>32</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" s="41" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="42" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" s="41" t="n">
-        <v>47</v>
-      </c>
-      <c r="J6" s="42" t="n">
-        <v>84</v>
-      </c>
-      <c r="K6" s="42" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" s="42" t="n">
-        <v>67</v>
-      </c>
-      <c r="M6" s="42" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>Pontlevoy</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="C7" s="41" t="n">
-        <v>35</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="n">
-        <v>66</v>
-      </c>
-      <c r="F7" s="42" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="42" t="n">
-        <v>70</v>
-      </c>
-      <c r="H7" s="42" t="n">
-        <v>90</v>
-      </c>
-      <c r="I7" s="42" t="n">
-        <v>52</v>
-      </c>
-      <c r="J7" s="42" t="n">
-        <v>81</v>
-      </c>
-      <c r="K7" s="41" t="n">
-        <v>34</v>
-      </c>
-      <c r="L7" s="41" t="n">
-        <v>46</v>
-      </c>
-      <c r="M7" s="42" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="C8" s="41" t="n">
-        <v>32</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>66</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="G8" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>61</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>99</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>85</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>96</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="40" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="41" t="n">
-        <v>48</v>
-      </c>
-      <c r="H9" s="41" t="n">
-        <v>46</v>
-      </c>
-      <c r="I9" s="41" t="n">
-        <v>33</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>70</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>65</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>74</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="40" t="inlineStr">
-        <is>
-          <t>Montoire-sur-le-Loir</t>
-        </is>
-      </c>
-      <c r="B10" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="C10" s="41" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" s="42" t="n">
-        <v>70</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <v>48</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>78</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>117</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>95</v>
-      </c>
-      <c r="L10" s="42" t="n">
-        <v>107</v>
-      </c>
-      <c r="M10" s="42" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>Cormenon</t>
-        </is>
-      </c>
-      <c r="B11" s="42" t="n">
-        <v>61</v>
-      </c>
-      <c r="C11" s="42" t="n">
-        <v>55</v>
-      </c>
-      <c r="D11" s="42" t="n">
-        <v>90</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>46</v>
-      </c>
-      <c r="G11" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>78</v>
-      </c>
-      <c r="J11" s="42" t="n">
-        <v>113</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>107</v>
-      </c>
-      <c r="L11" s="42" t="n">
-        <v>118</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="40" t="inlineStr">
-        <is>
-          <t>Crouy-sur-Cosson</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="C12" s="41" t="n">
-        <v>47</v>
-      </c>
-      <c r="D12" s="42" t="n">
-        <v>52</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>61</v>
-      </c>
-      <c r="F12" s="41" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>78</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>78</v>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="K12" s="41" t="n">
-        <v>41</v>
-      </c>
-      <c r="L12" s="41" t="n">
-        <v>47</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="40" t="inlineStr">
-        <is>
-          <t>Vouzon</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="n">
-        <v>65</v>
-      </c>
-      <c r="C13" s="42" t="n">
-        <v>84</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>81</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>99</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>70</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>117</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>113</v>
-      </c>
-      <c r="I13" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" s="41" t="n">
-        <v>49</v>
-      </c>
-      <c r="M13" s="41" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="40" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne</t>
-        </is>
-      </c>
-      <c r="B14" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="C14" s="42" t="n">
-        <v>55</v>
-      </c>
-      <c r="D14" s="41" t="n">
-        <v>34</v>
-      </c>
-      <c r="E14" s="42" t="n">
-        <v>85</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>65</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>95</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>107</v>
-      </c>
-      <c r="I14" s="41" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>54</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" s="41" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="B15" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="C15" s="42" t="n">
-        <v>67</v>
-      </c>
-      <c r="D15" s="41" t="n">
-        <v>46</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>96</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>74</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>107</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>118</v>
-      </c>
-      <c r="I15" s="41" t="n">
-        <v>47</v>
-      </c>
-      <c r="J15" s="41" t="n">
-        <v>49</v>
-      </c>
-      <c r="K15" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M15" s="34" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>La Ferté-Imbault</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="n">
-        <v>66</v>
-      </c>
-      <c r="C16" s="42" t="n">
-        <v>84</v>
-      </c>
-      <c r="D16" s="42" t="n">
-        <v>68</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>110</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>84</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>123</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>129</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>52</v>
-      </c>
-      <c r="J16" s="41" t="n">
-        <v>37</v>
-      </c>
-      <c r="K16" s="41" t="n">
-        <v>34</v>
-      </c>
-      <c r="L16" s="34" t="n">
-        <v>22</v>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Vert ≤ 30 km : enchaînement de deux demi-journées acceptable   ·   Orange 31-50 km : à éviter dans la même journée   ·   Rouge &gt; 50 km : incohérent</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>ENCHAÎNEMENTS RETENUS DANS LA GRILLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Matin</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Après-midi</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Techniciens concernés</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Montoire-sur-le-Loir</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Cormenon</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>30 km</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>T2 mardi, jeudi, samedi · T9 mardi</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>29 km</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>T2 lundi, mercredi, vendredi · T9 lundi, mercredi</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Épiais</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Vendôme</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>29 km</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>T11 mardi</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>La Ferté-Imbault</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>22 km</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>T3 mardi, jeudi, samedi · T10 vendredi</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Romorantin-Lanthenay</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Mur-de-Sologne</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>13 km</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>T10 lundi, mercredi</t>
         </is>
       </c>
     </row>
@@ -5420,7 +7198,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5828,7 +7605,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -5849,6 +7625,1445 @@
           <t>T11 est le renfort flottant : réserve pour les absences, les urgences et les pointes. Il est réaffecté chaque vendredi pour la semaine suivante.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMANDE PAR SECTEUR — DÉPARTEMENT 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Colonnes B à D : volumes bruts du fichier source. Colonne I (bleue) : volume SAV relevé sur votre planning hebdomadaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PROD octobre
+(inter./mois)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PROD mars
+(inter./mois)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>B2B
+(inter./mois)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mois retenu
+(max par secteur)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>PROD retenue
++10 % (/mois)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>PROD
++10 % (/sem.)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PROD
+(/sem.)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SAV
+(/sem.)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Demande totale
+(/sem.)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Créneaux cible
+(occupation 75 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>218</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="10">
+        <f>MAX($B5,$C5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
+        <f>($E5+$D5)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G5" s="30">
+        <f>$F5/4.3333</f>
+        <v/>
+      </c>
+      <c r="H5" s="30">
+        <f>$G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="J5" s="30">
+        <f>$H5+$I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="30">
+        <f>$J5/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E6" s="10">
+        <f>MAX($B6,$C6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>($E6+$D6)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>$F6/4.3333</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>$G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" s="30">
+        <f>$H6+$I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>$J6/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E7" s="10">
+        <f>MAX($B7,$C7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>($E7+$D7)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>$F7/4.3333</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>$G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" s="30">
+        <f>$H7+$I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="30">
+        <f>$J7/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E8" s="10">
+        <f>MAX($B8,$C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>($E8+$D8)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>$F8/4.3333</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>$G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="30">
+        <f>$H8+$I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>$J8/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E9" s="10">
+        <f>MAX($B9,$C9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>($E9+$D9)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>$F9/4.3333</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>$G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="30">
+        <f>$H9+$I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>$J9/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E10" s="10">
+        <f>MAX($B10,$C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>($E10+$D10)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>$F10/4.3333</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>$G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="30">
+        <f>$H10+$I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>$J10/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E11" s="10">
+        <f>MAX($B11,$C11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>($E11+$D11)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>$F11/4.3333</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>$G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="30">
+        <f>$H11+$I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>$J11/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E12" s="10">
+        <f>MAX($B12,$C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="30">
+        <f>($E12+$D12)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30">
+        <f>$F12/4.3333</f>
+        <v/>
+      </c>
+      <c r="H12" s="30">
+        <f>$G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="30">
+        <f>$H12+$I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="30">
+        <f>$J12/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E13" s="10">
+        <f>MAX($B13,$C13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="30">
+        <f>($E13+$D13)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="30">
+        <f>$F13/4.3333</f>
+        <v/>
+      </c>
+      <c r="H13" s="30">
+        <f>$G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="30">
+        <f>$H13+$I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="30">
+        <f>$J13/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E14" s="10">
+        <f>MAX($B14,$C14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>($E14+$D14)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>$F14/4.3333</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>$G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="30">
+        <f>$H14+$I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>$J14/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E15" s="10">
+        <f>MAX($B15,$C15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="30">
+        <f>($E15+$D15)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G15" s="30">
+        <f>$F15/4.3333</f>
+        <v/>
+      </c>
+      <c r="H15" s="30">
+        <f>$G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="30">
+        <f>$H15+$I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="30">
+        <f>$J15/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E16" s="10">
+        <f>MAX($B16,$C16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="30">
+        <f>($E16+$D16)*(1+Synthèse!$B$12)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30">
+        <f>$F16/4.3333</f>
+        <v/>
+      </c>
+      <c r="H16" s="30">
+        <f>$G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="30">
+        <f>$H16+$I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="30">
+        <f>$J16/Synthèse!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL DÉPARTEMENT 41</t>
+        </is>
+      </c>
+      <c r="B17" s="33">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="33">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="32">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
+        <f>SUM(E5:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="32">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="32">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="33">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="32">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="32">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Le fichier source ne dimensionne que sur mars. Or sur le 41, octobre est le mois haut (705 interventions contre 656) : retenir le mois le plus chargé secteur par secteur ajoute environ 7 % au besoin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MOTEUR DE DISPONIBILITÉ — RÉSERVATION SAV ET BASCULE PROD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le mécanisme qui libère de la disponibilité sans embaucher : on réserve large pour le SAV, et tout créneau non vendu redevient de la PROD la veille au soir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RÈGLES D'EXPLOITATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Moment</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Règle</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Effet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>La tournée est figée : technicien × jour × secteur ne change jamais.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Distances maîtrisées, techniciens sur des secteurs qu'ils connaissent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Chaque secteur est visité 3 fois par semaine, rythme Lundi-Mercredi-Vendredi ou Mardi-Jeudi-Samedi.</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Quel que soit le jour d'appel, il existe un passage à J+1 ou J+2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Sur chaque demi-journée, un nombre fixe de créneaux est réservé au SAV. Le reste est ouvert à la PROD.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>L'occupation ne dépasse jamais 75 % : le quart restant est la disponibilité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>J-7 à J-5</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>La PROD se pose uniquement sur les créneaux non réservés au SAV, dans le carnet J+5 à J+7.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Le client PROD obtient bien un RDV à J+5/J+6/J+7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>J-2, 18 h</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Ouverture à la prise de RDV SAV des créneaux réservés du jour J.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Le client SAV qui appelle voit de la dispo à J+1 et J+2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>J-1, 18 h</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>BASCULE : tout créneau SAV encore libre pour le lendemain est réaffecté à une intervention PROD du même secteur.</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Aucun créneau perdu. C'est ce qui rend la réservation SAV quasi gratuite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>J-1, 18 h</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>La bascule suppose au moins 2 interventions PROD en attente dans le secteur.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Sur Cormenon et La Ferté-Imbault, maintenir un stock PROD tampon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Jour J</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Un SAV urgent arrivé après la bascule prend la place d'une PROD du jour, qui repart en J+5.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>La PROD absorbe l'aléa, jamais le SAV — c'est elle qui a le délai le plus long.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Hebdo</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Si l'occupation SAV d'un secteur dépasse 75 % quatre semaines de suite, augmenter sa réservation.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Le curseur de réservation suit la demande réelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Hebdo</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Le renfort flottant (T11) est affecté le vendredi pour la semaine suivante, au secteur au carnet le plus tendu.</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>La réserve va là où elle sert, pas là où elle dort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TABLEAU DE BORD QUOTIDIEN — À REMPLIR CHAQUE SOIR AVANT LA BASCULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Colonne D (jaune) : nombre de RDV SAV réellement pris pour le lendemain. Le reste se calcule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Secteur visité demain</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Créneaux du jour</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>dont réservés SAV</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>RDV SAV pris (à saisir)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Créneaux SAV libres</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>PROD à injecter</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Occupation SAV</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Alerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Blois</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <f>MAX(0,$C20-$D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="7">
+        <f>$E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="37">
+        <f>IFERROR($D20/$C20,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="8">
+        <f>IF($D20&gt;$C20,"Débordement SAV : basculer une PROD du jour",IF($D20/$C20&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F20,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Pontlevoy</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7">
+        <f>MAX(0,$C21-$D21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>$E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="37">
+        <f>IFERROR($D21/$C21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="8">
+        <f>IF($D21&gt;$C21,"Débordement SAV : basculer une PROD du jour",IF($D21/$C21&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F21,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Vendôme</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7">
+        <f>MAX(0,$C22-$D22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="7">
+        <f>$E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="37">
+        <f>IFERROR($D22/$C22,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="8">
+        <f>IF($D22&gt;$C22,"Débordement SAV : basculer une PROD du jour",IF($D22/$C22&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F22,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Épiais</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7">
+        <f>MAX(0,$C23-$D23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="7">
+        <f>$E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="37">
+        <f>IFERROR($D23/$C23,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="8">
+        <f>IF($D23&gt;$C23,"Débordement SAV : basculer une PROD du jour",IF($D23/$C23&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F23,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Mur-de-Sologne</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <f>MAX(0,$C24-$D24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="7">
+        <f>$E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="37">
+        <f>IFERROR($D24/$C24,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="8">
+        <f>IF($D24&gt;$C24,"Débordement SAV : basculer une PROD du jour",IF($D24/$C24&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F24,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Crouy-sur-Cosson</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7">
+        <f>MAX(0,$C25-$D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="7">
+        <f>$E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="37">
+        <f>IFERROR($D25/$C25,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="8">
+        <f>IF($D25&gt;$C25,"Débordement SAV : basculer une PROD du jour",IF($D25/$C25&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F25,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Valencisse</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7">
+        <f>MAX(0,$C26-$D26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="7">
+        <f>$E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="37">
+        <f>IFERROR($D26/$C26,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="8">
+        <f>IF($D26&gt;$C26,"Débordement SAV : basculer une PROD du jour",IF($D26/$C26&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F26,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Montoire-sur-le-Loir</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7">
+        <f>MAX(0,$C27-$D27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="7">
+        <f>$E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="37">
+        <f>IFERROR($D27/$C27,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="8">
+        <f>IF($D27&gt;$C27,"Débordement SAV : basculer une PROD du jour",IF($D27/$C27&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F27,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Cormenon</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7">
+        <f>MAX(0,$C28-$D28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="7">
+        <f>$E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="37">
+        <f>IFERROR($D28/$C28,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="8">
+        <f>IF($D28&gt;$C28,"Débordement SAV : basculer une PROD du jour",IF($D28/$C28&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F28,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <f>MAX(0,$C29-$D29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="7">
+        <f>$E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="37">
+        <f>IFERROR($D29/$C29,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="8">
+        <f>IF($D29&gt;$C29,"Débordement SAV : basculer une PROD du jour",IF($D29/$C29&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F29,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>La Ferté-Imbault</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <f>MAX(0,$C30-$D30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="7">
+        <f>$E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="37">
+        <f>IFERROR($D30/$C30,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="8">
+        <f>IF($D30&gt;$C30,"Débordement SAV : basculer une PROD du jour",IF($D30/$C30&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F30,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Vouzon</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <f>MAX(0,$C31-$D31)</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>$E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="37">
+        <f>IFERROR($D31/$C31,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="8">
+        <f>IF($D31&gt;$C31,"Débordement SAV : basculer une PROD du jour",IF($D31/$C31&gt;0.75,"Occupation SAV &gt; 75 % : augmenter la réservation","Injecter "&amp;TEXT($F31,"0")&amp;" PROD du carnet J+5/J+7"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL JOUR</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>SUM(B20:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="4">
+        <f>SUM(C20:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>SUM(D20:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f>SUM(E20:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>SUM(F20:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="38">
+        <f>IFERROR($D32/$C32,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
